--- a/Mina_Stat_Formler/data_pipeline/styrfil_syss_kalkylator.xlsx
+++ b/Mina_Stat_Formler/data_pipeline/styrfil_syss_kalkylator.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SR-Disk-2\Hem0006\jimlin\Desktop\Mina_Befolknings_Dashboards\Mina_Stat_Formler\data_pipeline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Mina_Befolknings_Dashboards\Mina_Stat_Formler\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B432BB07-0316-4788-90C1-B0516FBA19E9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8B271D-4438-4D09-9E22-A345A44E689B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" activeTab="1" xr2:uid="{E0EECC81-014C-4A42-9525-5692D1E0B19F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" xr2:uid="{E0EECC81-014C-4A42-9525-5692D1E0B19F}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarier" sheetId="13" r:id="rId1"/>
@@ -23,9 +23,10 @@
     <sheet name="Tak_effekten" sheetId="17" r:id="rId8"/>
     <sheet name="Officiell_befolkningsprognos" sheetId="18" r:id="rId9"/>
     <sheet name="Matchning" sheetId="8" r:id="rId10"/>
-    <sheet name="Dummy" sheetId="6" r:id="rId11"/>
-    <sheet name="Flyttåldrar" sheetId="7" r:id="rId12"/>
-    <sheet name="Hushåll_referensperson" sheetId="10" r:id="rId13"/>
+    <sheet name="Rekryteringskvot" sheetId="19" r:id="rId11"/>
+    <sheet name="Dummy" sheetId="6" r:id="rId12"/>
+    <sheet name="Flyttåldrar" sheetId="7" r:id="rId13"/>
+    <sheet name="Hushåll_referensperson" sheetId="10" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="459">
   <si>
     <t>16-18 år</t>
   </si>
@@ -87,12 +88,6 @@
     <t>Nej</t>
   </si>
   <si>
-    <t>Matchning_transportmedel</t>
-  </si>
-  <si>
-    <t>Matchning_datateknik</t>
-  </si>
-  <si>
     <t>Referenspersons_ålder</t>
   </si>
   <si>
@@ -1110,12 +1105,6 @@
     <t>Privata tjänster</t>
   </si>
   <si>
-    <t>Privat tjänstekonsumtion</t>
-  </si>
-  <si>
-    <t>Näringslivets tjänstekonsumtion</t>
-  </si>
-  <si>
     <t>Okänt</t>
   </si>
   <si>
@@ -1330,6 +1319,102 @@
   </si>
   <si>
     <t>Just nu används endast kolumnerna Examinerade_studenter och Examinerade_Civilingenjörer i denna flik och då som under för att beräkna kvarstannandegrad</t>
+  </si>
+  <si>
+    <t>Branschkaraktär</t>
+  </si>
+  <si>
+    <t>Tillverkande</t>
+  </si>
+  <si>
+    <t>Ortstjänster</t>
+  </si>
+  <si>
+    <t>Företagsstödjande</t>
+  </si>
+  <si>
+    <t>Krympande</t>
+  </si>
+  <si>
+    <t>Varuproducerande</t>
+  </si>
+  <si>
+    <t>Konsumentinriktade tjänster</t>
+  </si>
+  <si>
+    <t>Näringslivslivstjänster</t>
+  </si>
+  <si>
+    <t>SSYK</t>
+  </si>
+  <si>
+    <t>Arbetslösa</t>
+  </si>
+  <si>
+    <t>Lediga jobb</t>
+  </si>
+  <si>
+    <t>Branschkoppling</t>
+  </si>
+  <si>
+    <t>Data/IT</t>
+  </si>
+  <si>
+    <t>Naturvetenskapligt arbete</t>
+  </si>
+  <si>
+    <t>Tekniskt arbete</t>
+  </si>
+  <si>
+    <t>Hälso- och sjukvård, eftergymnasial</t>
+  </si>
+  <si>
+    <t>Hälso- och sjukvård, gymnasial</t>
+  </si>
+  <si>
+    <t>Pendlingsförändring</t>
+  </si>
+  <si>
+    <t>Rekryteringskvot</t>
+  </si>
+  <si>
+    <t>Förgymnasial</t>
+  </si>
+  <si>
+    <t>Gymnasial</t>
+  </si>
+  <si>
+    <t>Eftergymnasial</t>
+  </si>
+  <si>
+    <t>Utbildningsnivå</t>
+  </si>
+  <si>
+    <t>Nya lediga jobb</t>
+  </si>
+  <si>
+    <t>Sysselsättningsförändring_dagbefolkning</t>
+  </si>
+  <si>
+    <t>Uppgift saknas</t>
+  </si>
+  <si>
+    <t>..</t>
+  </si>
+  <si>
+    <t>Bosättningskvot</t>
+  </si>
+  <si>
+    <t>Matchningskvot</t>
+  </si>
+  <si>
+    <t>Övriga</t>
+  </si>
+  <si>
+    <t>Bosättningskvot_%</t>
+  </si>
+  <si>
+    <t>Matchningskvot_%</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1421,6 +1506,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1748,27 +1839,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>298</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1783,15 +1874,15 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1803,12 +1894,12 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1823,12 +1914,12 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1843,12 +1934,12 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1865,7 +1956,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1897,12 +1988,12 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -1917,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -1931,144 +2022,2023 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="19.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>3</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>435</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1" t="s">
+        <v>444</v>
+      </c>
+      <c r="F1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H1" t="s">
+        <v>455</v>
+      </c>
+      <c r="I1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B2">
+        <v>2019</v>
+      </c>
+      <c r="D2">
+        <v>3192</v>
+      </c>
+      <c r="F2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G2">
+        <v>93</v>
+      </c>
+      <c r="H2">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B3">
+        <v>2020</v>
+      </c>
+      <c r="D3">
+        <v>3192</v>
+      </c>
+      <c r="F3">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G3">
+        <v>93</v>
+      </c>
+      <c r="H3">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B4">
+        <v>2021</v>
+      </c>
+      <c r="D4">
+        <v>3192</v>
+      </c>
+      <c r="F4">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G4">
+        <v>93</v>
+      </c>
+      <c r="H4">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B5">
+        <v>2022</v>
+      </c>
+      <c r="D5">
+        <v>3192</v>
+      </c>
+      <c r="F5">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G5">
+        <v>93</v>
+      </c>
+      <c r="H5">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B6">
+        <v>2023</v>
+      </c>
+      <c r="D6">
+        <v>3192</v>
+      </c>
+      <c r="F6">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G6">
+        <v>93</v>
+      </c>
+      <c r="H6">
+        <v>33</v>
+      </c>
+      <c r="I6" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="D7">
+        <v>3192</v>
+      </c>
+      <c r="F7">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G7">
+        <v>93</v>
+      </c>
+      <c r="H7">
+        <v>33</v>
+      </c>
+      <c r="I7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B8">
         <v>2025</v>
       </c>
-      <c r="B2" s="2">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="F8">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G8">
+        <v>93</v>
+      </c>
+      <c r="H8">
+        <v>33</v>
+      </c>
+      <c r="I8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9">
         <v>2026</v>
       </c>
-      <c r="B3" s="3">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="F9">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G9">
+        <v>93</v>
+      </c>
+      <c r="H9">
+        <v>33</v>
+      </c>
+      <c r="I9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B10">
         <v>2027</v>
       </c>
-      <c r="B4" s="3">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="F10">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G10">
+        <v>93</v>
+      </c>
+      <c r="H10">
+        <v>33</v>
+      </c>
+      <c r="I10" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11">
         <v>2028</v>
       </c>
-      <c r="B5" s="3">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="F11">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G11">
+        <v>93</v>
+      </c>
+      <c r="H11">
+        <v>33</v>
+      </c>
+      <c r="I11" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B12">
         <v>2029</v>
       </c>
-      <c r="B6" s="3">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="F12">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G12">
+        <v>93</v>
+      </c>
+      <c r="H12">
+        <v>33</v>
+      </c>
+      <c r="I12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B13">
         <v>2030</v>
       </c>
-      <c r="B7" s="3">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="F13">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G13">
+        <v>93</v>
+      </c>
+      <c r="H13">
+        <v>33</v>
+      </c>
+      <c r="I13" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B14">
         <v>2031</v>
       </c>
-      <c r="B8" s="3">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="F14">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G14">
+        <v>93</v>
+      </c>
+      <c r="H14">
+        <v>33</v>
+      </c>
+      <c r="I14" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B15">
         <v>2032</v>
       </c>
-      <c r="B9" s="3">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="F15">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G15">
+        <v>93</v>
+      </c>
+      <c r="H15">
+        <v>33</v>
+      </c>
+      <c r="I15" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B16">
         <v>2033</v>
       </c>
-      <c r="B10" s="3">
-        <v>10</v>
-      </c>
-      <c r="C10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="F16">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G16">
+        <v>93</v>
+      </c>
+      <c r="H16">
+        <v>33</v>
+      </c>
+      <c r="I16" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B17">
         <v>2034</v>
       </c>
-      <c r="B11" s="3">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="F17">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G17">
+        <v>93</v>
+      </c>
+      <c r="H17">
+        <v>33</v>
+      </c>
+      <c r="I17" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B18">
         <v>2035</v>
       </c>
-      <c r="B12" s="3">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>10</v>
+      <c r="F18">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G18">
+        <v>93</v>
+      </c>
+      <c r="H18">
+        <v>33</v>
+      </c>
+      <c r="I18" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B19">
+        <v>2019</v>
+      </c>
+      <c r="D19">
+        <v>349</v>
+      </c>
+      <c r="F19">
+        <v>3.8</v>
+      </c>
+      <c r="G19">
+        <v>74</v>
+      </c>
+      <c r="H19">
+        <v>29</v>
+      </c>
+      <c r="I19" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B20">
+        <v>2020</v>
+      </c>
+      <c r="D20">
+        <v>349</v>
+      </c>
+      <c r="F20">
+        <v>3.8</v>
+      </c>
+      <c r="G20">
+        <v>74</v>
+      </c>
+      <c r="H20">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B21">
+        <v>2021</v>
+      </c>
+      <c r="D21">
+        <v>349</v>
+      </c>
+      <c r="F21">
+        <v>3.8</v>
+      </c>
+      <c r="G21">
+        <v>74</v>
+      </c>
+      <c r="H21">
+        <v>29</v>
+      </c>
+      <c r="I21" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B22">
+        <v>2022</v>
+      </c>
+      <c r="D22">
+        <v>349</v>
+      </c>
+      <c r="F22">
+        <v>3.8</v>
+      </c>
+      <c r="G22">
+        <v>74</v>
+      </c>
+      <c r="H22">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B23">
+        <v>2023</v>
+      </c>
+      <c r="D23">
+        <v>349</v>
+      </c>
+      <c r="F23">
+        <v>3.8</v>
+      </c>
+      <c r="G23">
+        <v>74</v>
+      </c>
+      <c r="H23">
+        <v>29</v>
+      </c>
+      <c r="I23" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B24">
+        <v>2024</v>
+      </c>
+      <c r="D24">
+        <v>349</v>
+      </c>
+      <c r="F24">
+        <v>3.8</v>
+      </c>
+      <c r="G24">
+        <v>74</v>
+      </c>
+      <c r="H24">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B25">
+        <v>2025</v>
+      </c>
+      <c r="F25">
+        <v>3.8</v>
+      </c>
+      <c r="G25">
+        <v>74</v>
+      </c>
+      <c r="H25">
+        <v>29</v>
+      </c>
+      <c r="I25" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B26">
+        <v>2026</v>
+      </c>
+      <c r="F26">
+        <v>3.8</v>
+      </c>
+      <c r="G26">
+        <v>74</v>
+      </c>
+      <c r="H26">
+        <v>29</v>
+      </c>
+      <c r="I26" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B27">
+        <v>2027</v>
+      </c>
+      <c r="F27">
+        <v>3.8</v>
+      </c>
+      <c r="G27">
+        <v>74</v>
+      </c>
+      <c r="H27">
+        <v>29</v>
+      </c>
+      <c r="I27" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B28">
+        <v>2028</v>
+      </c>
+      <c r="F28">
+        <v>3.8</v>
+      </c>
+      <c r="G28">
+        <v>74</v>
+      </c>
+      <c r="H28">
+        <v>29</v>
+      </c>
+      <c r="I28" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B29">
+        <v>2029</v>
+      </c>
+      <c r="F29">
+        <v>3.8</v>
+      </c>
+      <c r="G29">
+        <v>74</v>
+      </c>
+      <c r="H29">
+        <v>29</v>
+      </c>
+      <c r="I29" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B30">
+        <v>2030</v>
+      </c>
+      <c r="F30">
+        <v>3.8</v>
+      </c>
+      <c r="G30">
+        <v>74</v>
+      </c>
+      <c r="H30">
+        <v>29</v>
+      </c>
+      <c r="I30" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B31">
+        <v>2031</v>
+      </c>
+      <c r="F31">
+        <v>3.8</v>
+      </c>
+      <c r="G31">
+        <v>74</v>
+      </c>
+      <c r="H31">
+        <v>29</v>
+      </c>
+      <c r="I31" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B32">
+        <v>2032</v>
+      </c>
+      <c r="F32">
+        <v>3.8</v>
+      </c>
+      <c r="G32">
+        <v>74</v>
+      </c>
+      <c r="H32">
+        <v>29</v>
+      </c>
+      <c r="I32" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B33">
+        <v>2033</v>
+      </c>
+      <c r="F33">
+        <v>3.8</v>
+      </c>
+      <c r="G33">
+        <v>74</v>
+      </c>
+      <c r="H33">
+        <v>29</v>
+      </c>
+      <c r="I33" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B34">
+        <v>2034</v>
+      </c>
+      <c r="F34">
+        <v>3.8</v>
+      </c>
+      <c r="G34">
+        <v>74</v>
+      </c>
+      <c r="H34">
+        <v>29</v>
+      </c>
+      <c r="I34" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B35">
+        <v>2035</v>
+      </c>
+      <c r="F35">
+        <v>3.8</v>
+      </c>
+      <c r="G35">
+        <v>74</v>
+      </c>
+      <c r="H35">
+        <v>29</v>
+      </c>
+      <c r="I35" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B36">
+        <v>2019</v>
+      </c>
+      <c r="D36">
+        <v>1679</v>
+      </c>
+      <c r="F36">
+        <v>7.9</v>
+      </c>
+      <c r="G36">
+        <v>82</v>
+      </c>
+      <c r="H36">
+        <v>19</v>
+      </c>
+      <c r="I36" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B37">
+        <v>2020</v>
+      </c>
+      <c r="D37">
+        <v>1679</v>
+      </c>
+      <c r="F37">
+        <v>7.9</v>
+      </c>
+      <c r="G37">
+        <v>82</v>
+      </c>
+      <c r="H37">
+        <v>19</v>
+      </c>
+      <c r="I37" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B38">
+        <v>2021</v>
+      </c>
+      <c r="D38">
+        <v>1679</v>
+      </c>
+      <c r="F38">
+        <v>7.9</v>
+      </c>
+      <c r="G38">
+        <v>82</v>
+      </c>
+      <c r="H38">
+        <v>19</v>
+      </c>
+      <c r="I38" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B39">
+        <v>2022</v>
+      </c>
+      <c r="D39">
+        <v>1679</v>
+      </c>
+      <c r="F39">
+        <v>7.9</v>
+      </c>
+      <c r="G39">
+        <v>82</v>
+      </c>
+      <c r="H39">
+        <v>19</v>
+      </c>
+      <c r="I39" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B40">
+        <v>2023</v>
+      </c>
+      <c r="D40">
+        <v>1679</v>
+      </c>
+      <c r="F40">
+        <v>7.9</v>
+      </c>
+      <c r="G40">
+        <v>82</v>
+      </c>
+      <c r="H40">
+        <v>19</v>
+      </c>
+      <c r="I40" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B41">
+        <v>2024</v>
+      </c>
+      <c r="D41">
+        <v>1679</v>
+      </c>
+      <c r="F41">
+        <v>7.9</v>
+      </c>
+      <c r="G41">
+        <v>82</v>
+      </c>
+      <c r="H41">
+        <v>19</v>
+      </c>
+      <c r="I41" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B42">
+        <v>2025</v>
+      </c>
+      <c r="F42">
+        <v>7.9</v>
+      </c>
+      <c r="G42">
+        <v>82</v>
+      </c>
+      <c r="H42">
+        <v>19</v>
+      </c>
+      <c r="I42" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B43">
+        <v>2026</v>
+      </c>
+      <c r="F43">
+        <v>7.9</v>
+      </c>
+      <c r="G43">
+        <v>82</v>
+      </c>
+      <c r="H43">
+        <v>19</v>
+      </c>
+      <c r="I43" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B44">
+        <v>2027</v>
+      </c>
+      <c r="F44">
+        <v>7.9</v>
+      </c>
+      <c r="G44">
+        <v>82</v>
+      </c>
+      <c r="H44">
+        <v>19</v>
+      </c>
+      <c r="I44" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B45">
+        <v>2028</v>
+      </c>
+      <c r="F45">
+        <v>7.9</v>
+      </c>
+      <c r="G45">
+        <v>82</v>
+      </c>
+      <c r="H45">
+        <v>19</v>
+      </c>
+      <c r="I45" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B46">
+        <v>2029</v>
+      </c>
+      <c r="F46">
+        <v>7.9</v>
+      </c>
+      <c r="G46">
+        <v>82</v>
+      </c>
+      <c r="H46">
+        <v>19</v>
+      </c>
+      <c r="I46" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B47">
+        <v>2030</v>
+      </c>
+      <c r="F47">
+        <v>7.9</v>
+      </c>
+      <c r="G47">
+        <v>82</v>
+      </c>
+      <c r="H47">
+        <v>19</v>
+      </c>
+      <c r="I47" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B48">
+        <v>2031</v>
+      </c>
+      <c r="F48">
+        <v>7.9</v>
+      </c>
+      <c r="G48">
+        <v>82</v>
+      </c>
+      <c r="H48">
+        <v>19</v>
+      </c>
+      <c r="I48" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B49">
+        <v>2032</v>
+      </c>
+      <c r="F49">
+        <v>7.9</v>
+      </c>
+      <c r="G49">
+        <v>82</v>
+      </c>
+      <c r="H49">
+        <v>19</v>
+      </c>
+      <c r="I49" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B50">
+        <v>2033</v>
+      </c>
+      <c r="F50">
+        <v>7.9</v>
+      </c>
+      <c r="G50">
+        <v>82</v>
+      </c>
+      <c r="H50">
+        <v>19</v>
+      </c>
+      <c r="I50" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B51">
+        <v>2034</v>
+      </c>
+      <c r="F51">
+        <v>7.9</v>
+      </c>
+      <c r="G51">
+        <v>82</v>
+      </c>
+      <c r="H51">
+        <v>19</v>
+      </c>
+      <c r="I51" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B52">
+        <v>2035</v>
+      </c>
+      <c r="F52">
+        <v>7.9</v>
+      </c>
+      <c r="G52">
+        <v>82</v>
+      </c>
+      <c r="H52">
+        <v>19</v>
+      </c>
+      <c r="I52" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B53">
+        <v>2019</v>
+      </c>
+      <c r="D53">
+        <v>3211</v>
+      </c>
+      <c r="F53">
+        <v>31.8</v>
+      </c>
+      <c r="G53">
+        <v>52</v>
+      </c>
+      <c r="H53">
+        <v>13</v>
+      </c>
+      <c r="I53" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B54">
+        <v>2020</v>
+      </c>
+      <c r="D54">
+        <v>3211</v>
+      </c>
+      <c r="F54">
+        <v>31.8</v>
+      </c>
+      <c r="G54">
+        <v>52</v>
+      </c>
+      <c r="H54">
+        <v>13</v>
+      </c>
+      <c r="I54" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B55">
+        <v>2021</v>
+      </c>
+      <c r="D55">
+        <v>3211</v>
+      </c>
+      <c r="F55">
+        <v>31.8</v>
+      </c>
+      <c r="G55">
+        <v>52</v>
+      </c>
+      <c r="H55">
+        <v>13</v>
+      </c>
+      <c r="I55" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B56">
+        <v>2022</v>
+      </c>
+      <c r="D56">
+        <v>3211</v>
+      </c>
+      <c r="F56">
+        <v>31.8</v>
+      </c>
+      <c r="G56">
+        <v>52</v>
+      </c>
+      <c r="H56">
+        <v>13</v>
+      </c>
+      <c r="I56" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B57">
+        <v>2023</v>
+      </c>
+      <c r="D57">
+        <v>3211</v>
+      </c>
+      <c r="F57">
+        <v>31.8</v>
+      </c>
+      <c r="G57">
+        <v>52</v>
+      </c>
+      <c r="H57">
+        <v>13</v>
+      </c>
+      <c r="I57" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="B58">
+        <v>2024</v>
+      </c>
+      <c r="D58">
+        <v>3211</v>
+      </c>
+      <c r="F58">
+        <v>31.8</v>
+      </c>
+      <c r="G58">
+        <v>52</v>
+      </c>
+      <c r="H58">
+        <v>13</v>
+      </c>
+      <c r="I58" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B59">
+        <v>2025</v>
+      </c>
+      <c r="F59">
+        <v>31.8</v>
+      </c>
+      <c r="G59">
+        <v>52</v>
+      </c>
+      <c r="H59">
+        <v>13</v>
+      </c>
+      <c r="I59" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B60">
+        <v>2026</v>
+      </c>
+      <c r="F60">
+        <v>31.8</v>
+      </c>
+      <c r="G60">
+        <v>52</v>
+      </c>
+      <c r="H60">
+        <v>13</v>
+      </c>
+      <c r="I60" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B61">
+        <v>2027</v>
+      </c>
+      <c r="F61">
+        <v>31.8</v>
+      </c>
+      <c r="G61">
+        <v>52</v>
+      </c>
+      <c r="H61">
+        <v>13</v>
+      </c>
+      <c r="I61" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B62">
+        <v>2028</v>
+      </c>
+      <c r="F62">
+        <v>31.8</v>
+      </c>
+      <c r="G62">
+        <v>52</v>
+      </c>
+      <c r="H62">
+        <v>13</v>
+      </c>
+      <c r="I62" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B63">
+        <v>2029</v>
+      </c>
+      <c r="F63">
+        <v>31.8</v>
+      </c>
+      <c r="G63">
+        <v>52</v>
+      </c>
+      <c r="H63">
+        <v>13</v>
+      </c>
+      <c r="I63" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B64">
+        <v>2030</v>
+      </c>
+      <c r="F64">
+        <v>31.8</v>
+      </c>
+      <c r="G64">
+        <v>52</v>
+      </c>
+      <c r="H64">
+        <v>13</v>
+      </c>
+      <c r="I64" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B65">
+        <v>2031</v>
+      </c>
+      <c r="F65">
+        <v>31.8</v>
+      </c>
+      <c r="G65">
+        <v>52</v>
+      </c>
+      <c r="H65">
+        <v>13</v>
+      </c>
+      <c r="I65" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B66">
+        <v>2032</v>
+      </c>
+      <c r="F66">
+        <v>31.8</v>
+      </c>
+      <c r="G66">
+        <v>52</v>
+      </c>
+      <c r="H66">
+        <v>13</v>
+      </c>
+      <c r="I66" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B67">
+        <v>2033</v>
+      </c>
+      <c r="F67">
+        <v>31.8</v>
+      </c>
+      <c r="G67">
+        <v>52</v>
+      </c>
+      <c r="H67">
+        <v>13</v>
+      </c>
+      <c r="I67" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B68">
+        <v>2034</v>
+      </c>
+      <c r="F68">
+        <v>31.8</v>
+      </c>
+      <c r="G68">
+        <v>52</v>
+      </c>
+      <c r="H68">
+        <v>13</v>
+      </c>
+      <c r="I68" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B69">
+        <v>2035</v>
+      </c>
+      <c r="F69">
+        <v>31.8</v>
+      </c>
+      <c r="G69">
+        <v>52</v>
+      </c>
+      <c r="H69">
+        <v>13</v>
+      </c>
+      <c r="I69" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B70">
+        <v>2019</v>
+      </c>
+      <c r="D70">
+        <v>3617</v>
+      </c>
+      <c r="F70">
+        <v>26.1</v>
+      </c>
+      <c r="G70">
+        <v>76</v>
+      </c>
+      <c r="H70">
+        <v>13</v>
+      </c>
+      <c r="I70" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B71">
+        <v>2020</v>
+      </c>
+      <c r="D71">
+        <v>3617</v>
+      </c>
+      <c r="F71">
+        <v>26.1</v>
+      </c>
+      <c r="G71">
+        <v>76</v>
+      </c>
+      <c r="H71">
+        <v>13</v>
+      </c>
+      <c r="I71" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B72">
+        <v>2021</v>
+      </c>
+      <c r="D72">
+        <v>3617</v>
+      </c>
+      <c r="F72">
+        <v>26.1</v>
+      </c>
+      <c r="G72">
+        <v>76</v>
+      </c>
+      <c r="H72">
+        <v>13</v>
+      </c>
+      <c r="I72" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B73">
+        <v>2022</v>
+      </c>
+      <c r="D73">
+        <v>3617</v>
+      </c>
+      <c r="F73">
+        <v>26.1</v>
+      </c>
+      <c r="G73">
+        <v>76</v>
+      </c>
+      <c r="H73">
+        <v>13</v>
+      </c>
+      <c r="I73" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B74">
+        <v>2023</v>
+      </c>
+      <c r="D74">
+        <v>3617</v>
+      </c>
+      <c r="F74">
+        <v>26.1</v>
+      </c>
+      <c r="G74">
+        <v>76</v>
+      </c>
+      <c r="H74">
+        <v>13</v>
+      </c>
+      <c r="I74" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="B75">
+        <v>2024</v>
+      </c>
+      <c r="D75">
+        <v>3617</v>
+      </c>
+      <c r="F75">
+        <v>26.1</v>
+      </c>
+      <c r="G75">
+        <v>76</v>
+      </c>
+      <c r="H75">
+        <v>13</v>
+      </c>
+      <c r="I75" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B76">
+        <v>2025</v>
+      </c>
+      <c r="F76">
+        <v>26.1</v>
+      </c>
+      <c r="G76">
+        <v>76</v>
+      </c>
+      <c r="H76">
+        <v>13</v>
+      </c>
+      <c r="I76" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B77">
+        <v>2026</v>
+      </c>
+      <c r="F77">
+        <v>26.1</v>
+      </c>
+      <c r="G77">
+        <v>76</v>
+      </c>
+      <c r="H77">
+        <v>13</v>
+      </c>
+      <c r="I77" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B78">
+        <v>2027</v>
+      </c>
+      <c r="F78">
+        <v>26.1</v>
+      </c>
+      <c r="G78">
+        <v>76</v>
+      </c>
+      <c r="H78">
+        <v>13</v>
+      </c>
+      <c r="I78" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B79">
+        <v>2028</v>
+      </c>
+      <c r="F79">
+        <v>26.1</v>
+      </c>
+      <c r="G79">
+        <v>76</v>
+      </c>
+      <c r="H79">
+        <v>13</v>
+      </c>
+      <c r="I79" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B80">
+        <v>2029</v>
+      </c>
+      <c r="F80">
+        <v>26.1</v>
+      </c>
+      <c r="G80">
+        <v>76</v>
+      </c>
+      <c r="H80">
+        <v>13</v>
+      </c>
+      <c r="I80" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B81">
+        <v>2030</v>
+      </c>
+      <c r="F81">
+        <v>26.1</v>
+      </c>
+      <c r="G81">
+        <v>76</v>
+      </c>
+      <c r="H81">
+        <v>13</v>
+      </c>
+      <c r="I81" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B82">
+        <v>2031</v>
+      </c>
+      <c r="F82">
+        <v>26.1</v>
+      </c>
+      <c r="G82">
+        <v>76</v>
+      </c>
+      <c r="H82">
+        <v>13</v>
+      </c>
+      <c r="I82" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B83">
+        <v>2032</v>
+      </c>
+      <c r="F83">
+        <v>26.1</v>
+      </c>
+      <c r="G83">
+        <v>76</v>
+      </c>
+      <c r="H83">
+        <v>13</v>
+      </c>
+      <c r="I83" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B84">
+        <v>2033</v>
+      </c>
+      <c r="F84">
+        <v>26.1</v>
+      </c>
+      <c r="G84">
+        <v>76</v>
+      </c>
+      <c r="H84">
+        <v>13</v>
+      </c>
+      <c r="I84" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B85">
+        <v>2034</v>
+      </c>
+      <c r="F85">
+        <v>26.1</v>
+      </c>
+      <c r="G85">
+        <v>76</v>
+      </c>
+      <c r="H85">
+        <v>13</v>
+      </c>
+      <c r="I85" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B86">
+        <v>2035</v>
+      </c>
+      <c r="F86">
+        <v>26.1</v>
+      </c>
+      <c r="G86">
+        <v>76</v>
+      </c>
+      <c r="H86">
+        <v>13</v>
+      </c>
+      <c r="I86" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B87">
+        <v>2020</v>
+      </c>
+      <c r="F87">
+        <v>26.1</v>
+      </c>
+      <c r="G87">
+        <v>76</v>
+      </c>
+      <c r="H87">
+        <v>13</v>
+      </c>
+      <c r="I87" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B88">
+        <v>2021</v>
+      </c>
+      <c r="F88">
+        <v>26.1</v>
+      </c>
+      <c r="G88">
+        <v>76</v>
+      </c>
+      <c r="H88">
+        <v>13</v>
+      </c>
+      <c r="I88" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B89">
+        <v>2022</v>
+      </c>
+      <c r="F89">
+        <v>26.1</v>
+      </c>
+      <c r="G89">
+        <v>76</v>
+      </c>
+      <c r="H89">
+        <v>13</v>
+      </c>
+      <c r="I89" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B90">
+        <v>2023</v>
+      </c>
+      <c r="F90">
+        <v>26.1</v>
+      </c>
+      <c r="G90">
+        <v>76</v>
+      </c>
+      <c r="H90">
+        <v>13</v>
+      </c>
+      <c r="I90" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="B91">
+        <v>2024</v>
+      </c>
+      <c r="F91">
+        <v>26.1</v>
+      </c>
+      <c r="G91">
+        <v>76</v>
+      </c>
+      <c r="H91">
+        <v>13</v>
+      </c>
+      <c r="I91" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B92">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B93">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B94">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B95">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B96">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B97">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B98">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B99">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B100">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B101">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B102">
+        <v>2035</v>
       </c>
     </row>
   </sheetData>
@@ -2077,6 +4047,1682 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB67651-1C6E-4C6B-A906-335CF34069BD}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:G86"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1" t="s">
+        <v>445</v>
+      </c>
+      <c r="F1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B2">
+        <v>2019</v>
+      </c>
+      <c r="C2">
+        <v>1232</v>
+      </c>
+      <c r="D2">
+        <v>57</v>
+      </c>
+      <c r="E2" s="5">
+        <f t="shared" ref="E2:E7" si="0">SUM(C2/D2)</f>
+        <v>21.614035087719298</v>
+      </c>
+      <c r="F2">
+        <v>151</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B3">
+        <v>2020</v>
+      </c>
+      <c r="C3">
+        <v>1232</v>
+      </c>
+      <c r="D3">
+        <v>57</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" si="0"/>
+        <v>21.614035087719298</v>
+      </c>
+      <c r="F3">
+        <v>151</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B4">
+        <v>2021</v>
+      </c>
+      <c r="C4">
+        <v>1232</v>
+      </c>
+      <c r="D4">
+        <v>57</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>21.614035087719298</v>
+      </c>
+      <c r="F4">
+        <v>151</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>446</v>
+      </c>
+      <c r="B5">
+        <v>2022</v>
+      </c>
+      <c r="C5">
+        <v>1232</v>
+      </c>
+      <c r="D5">
+        <v>57</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>21.614035087719298</v>
+      </c>
+      <c r="F5">
+        <v>151</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B6">
+        <v>2023</v>
+      </c>
+      <c r="C6">
+        <v>1232</v>
+      </c>
+      <c r="D6">
+        <v>57</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>21.614035087719298</v>
+      </c>
+      <c r="F6">
+        <v>151</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>446</v>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>1232</v>
+      </c>
+      <c r="D7">
+        <v>57</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>21.614035087719298</v>
+      </c>
+      <c r="F7">
+        <v>151</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>446</v>
+      </c>
+      <c r="B8">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F8">
+        <v>151</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>446</v>
+      </c>
+      <c r="B9">
+        <v>2026</v>
+      </c>
+      <c r="E9" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F9">
+        <v>151</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B10">
+        <v>2027</v>
+      </c>
+      <c r="E10" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F10">
+        <v>151</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>446</v>
+      </c>
+      <c r="B11">
+        <v>2028</v>
+      </c>
+      <c r="E11" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F11">
+        <v>151</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>446</v>
+      </c>
+      <c r="B12">
+        <v>2029</v>
+      </c>
+      <c r="E12" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F12">
+        <v>151</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>446</v>
+      </c>
+      <c r="B13">
+        <v>2030</v>
+      </c>
+      <c r="E13" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F13">
+        <v>151</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>446</v>
+      </c>
+      <c r="B14">
+        <v>2031</v>
+      </c>
+      <c r="E14" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F14">
+        <v>151</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>446</v>
+      </c>
+      <c r="B15">
+        <v>2032</v>
+      </c>
+      <c r="E15" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F15">
+        <v>151</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>446</v>
+      </c>
+      <c r="B16">
+        <v>2033</v>
+      </c>
+      <c r="E16" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F16">
+        <v>151</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>446</v>
+      </c>
+      <c r="B17">
+        <v>2034</v>
+      </c>
+      <c r="E17" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F17">
+        <v>151</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>446</v>
+      </c>
+      <c r="B18">
+        <v>2035</v>
+      </c>
+      <c r="E18" s="5">
+        <v>21.744117647058822</v>
+      </c>
+      <c r="F18">
+        <v>151</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B19">
+        <v>2019</v>
+      </c>
+      <c r="C19">
+        <v>12953</v>
+      </c>
+      <c r="D19">
+        <v>19</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" ref="E19:E24" si="1">SUM(C19/D19)</f>
+        <v>681.73684210526312</v>
+      </c>
+      <c r="F19">
+        <v>-520</v>
+      </c>
+      <c r="G19">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>447</v>
+      </c>
+      <c r="B20">
+        <v>2020</v>
+      </c>
+      <c r="C20">
+        <v>12953</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="1"/>
+        <v>681.73684210526312</v>
+      </c>
+      <c r="F20">
+        <v>-520</v>
+      </c>
+      <c r="G20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>447</v>
+      </c>
+      <c r="B21">
+        <v>2021</v>
+      </c>
+      <c r="C21">
+        <v>12953</v>
+      </c>
+      <c r="D21">
+        <v>19</v>
+      </c>
+      <c r="E21" s="5">
+        <f t="shared" si="1"/>
+        <v>681.73684210526312</v>
+      </c>
+      <c r="F21">
+        <v>-520</v>
+      </c>
+      <c r="G21">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>447</v>
+      </c>
+      <c r="B22">
+        <v>2022</v>
+      </c>
+      <c r="C22">
+        <v>12953</v>
+      </c>
+      <c r="D22">
+        <v>19</v>
+      </c>
+      <c r="E22" s="5">
+        <f t="shared" si="1"/>
+        <v>681.73684210526312</v>
+      </c>
+      <c r="F22">
+        <v>-520</v>
+      </c>
+      <c r="G22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>447</v>
+      </c>
+      <c r="B23">
+        <v>2023</v>
+      </c>
+      <c r="C23">
+        <v>12953</v>
+      </c>
+      <c r="D23">
+        <v>19</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="1"/>
+        <v>681.73684210526312</v>
+      </c>
+      <c r="F23">
+        <v>-520</v>
+      </c>
+      <c r="G23">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>447</v>
+      </c>
+      <c r="B24">
+        <v>2024</v>
+      </c>
+      <c r="C24">
+        <v>12953</v>
+      </c>
+      <c r="D24">
+        <v>19</v>
+      </c>
+      <c r="E24" s="5">
+        <f t="shared" si="1"/>
+        <v>681.73684210526312</v>
+      </c>
+      <c r="F24">
+        <v>-520</v>
+      </c>
+      <c r="G24">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>447</v>
+      </c>
+      <c r="B25">
+        <v>2025</v>
+      </c>
+      <c r="E25" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F25">
+        <v>-520</v>
+      </c>
+      <c r="G25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>447</v>
+      </c>
+      <c r="B26">
+        <v>2026</v>
+      </c>
+      <c r="E26" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F26">
+        <v>-520</v>
+      </c>
+      <c r="G26">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>447</v>
+      </c>
+      <c r="B27">
+        <v>2027</v>
+      </c>
+      <c r="E27" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F27">
+        <v>-520</v>
+      </c>
+      <c r="G27">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>447</v>
+      </c>
+      <c r="B28">
+        <v>2028</v>
+      </c>
+      <c r="E28" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F28">
+        <v>-520</v>
+      </c>
+      <c r="G28">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>447</v>
+      </c>
+      <c r="B29">
+        <v>2029</v>
+      </c>
+      <c r="E29" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F29">
+        <v>-520</v>
+      </c>
+      <c r="G29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>447</v>
+      </c>
+      <c r="B30">
+        <v>2030</v>
+      </c>
+      <c r="E30" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F30">
+        <v>-520</v>
+      </c>
+      <c r="G30">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>447</v>
+      </c>
+      <c r="B31">
+        <v>2031</v>
+      </c>
+      <c r="E31" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F31">
+        <v>-520</v>
+      </c>
+      <c r="G31">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>447</v>
+      </c>
+      <c r="B32">
+        <v>2032</v>
+      </c>
+      <c r="E32" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F32">
+        <v>-520</v>
+      </c>
+      <c r="G32">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>447</v>
+      </c>
+      <c r="B33">
+        <v>2033</v>
+      </c>
+      <c r="E33" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F33">
+        <v>-520</v>
+      </c>
+      <c r="G33">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>447</v>
+      </c>
+      <c r="B34">
+        <v>2034</v>
+      </c>
+      <c r="E34" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F34">
+        <v>-520</v>
+      </c>
+      <c r="G34">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>447</v>
+      </c>
+      <c r="B35">
+        <v>2035</v>
+      </c>
+      <c r="E35" s="5">
+        <v>700.17117117117118</v>
+      </c>
+      <c r="F35">
+        <v>-520</v>
+      </c>
+      <c r="G35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>448</v>
+      </c>
+      <c r="B36">
+        <v>2019</v>
+      </c>
+      <c r="C36">
+        <v>14514</v>
+      </c>
+      <c r="D36">
+        <v>1317</v>
+      </c>
+      <c r="E36" s="5">
+        <f t="shared" ref="E36:E41" si="2">SUM(C36/D36)</f>
+        <v>11.020501138952165</v>
+      </c>
+      <c r="F36">
+        <v>78</v>
+      </c>
+      <c r="G36">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>448</v>
+      </c>
+      <c r="B37">
+        <v>2020</v>
+      </c>
+      <c r="C37">
+        <v>14514</v>
+      </c>
+      <c r="D37">
+        <v>1317</v>
+      </c>
+      <c r="E37" s="5">
+        <f t="shared" si="2"/>
+        <v>11.020501138952165</v>
+      </c>
+      <c r="F37">
+        <v>78</v>
+      </c>
+      <c r="G37">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>448</v>
+      </c>
+      <c r="B38">
+        <v>2021</v>
+      </c>
+      <c r="C38">
+        <v>14514</v>
+      </c>
+      <c r="D38">
+        <v>1317</v>
+      </c>
+      <c r="E38" s="5">
+        <f t="shared" si="2"/>
+        <v>11.020501138952165</v>
+      </c>
+      <c r="F38">
+        <v>78</v>
+      </c>
+      <c r="G38">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>448</v>
+      </c>
+      <c r="B39">
+        <v>2022</v>
+      </c>
+      <c r="C39">
+        <v>14514</v>
+      </c>
+      <c r="D39">
+        <v>1317</v>
+      </c>
+      <c r="E39" s="5">
+        <f t="shared" si="2"/>
+        <v>11.020501138952165</v>
+      </c>
+      <c r="F39">
+        <v>78</v>
+      </c>
+      <c r="G39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>448</v>
+      </c>
+      <c r="B40">
+        <v>2023</v>
+      </c>
+      <c r="C40">
+        <v>14514</v>
+      </c>
+      <c r="D40">
+        <v>1317</v>
+      </c>
+      <c r="E40" s="5">
+        <f t="shared" si="2"/>
+        <v>11.020501138952165</v>
+      </c>
+      <c r="F40">
+        <v>78</v>
+      </c>
+      <c r="G40">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>448</v>
+      </c>
+      <c r="B41">
+        <v>2024</v>
+      </c>
+      <c r="C41">
+        <v>14514</v>
+      </c>
+      <c r="D41">
+        <v>1317</v>
+      </c>
+      <c r="E41" s="5">
+        <f t="shared" si="2"/>
+        <v>11.020501138952165</v>
+      </c>
+      <c r="F41">
+        <v>78</v>
+      </c>
+      <c r="G41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>448</v>
+      </c>
+      <c r="B42">
+        <v>2025</v>
+      </c>
+      <c r="E42" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F42">
+        <v>78</v>
+      </c>
+      <c r="G42">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>448</v>
+      </c>
+      <c r="B43">
+        <v>2026</v>
+      </c>
+      <c r="E43" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F43">
+        <v>78</v>
+      </c>
+      <c r="G43">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>448</v>
+      </c>
+      <c r="B44">
+        <v>2027</v>
+      </c>
+      <c r="E44" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F44">
+        <v>78</v>
+      </c>
+      <c r="G44">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>448</v>
+      </c>
+      <c r="B45">
+        <v>2028</v>
+      </c>
+      <c r="E45" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F45">
+        <v>78</v>
+      </c>
+      <c r="G45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>448</v>
+      </c>
+      <c r="B46">
+        <v>2029</v>
+      </c>
+      <c r="E46" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F46">
+        <v>78</v>
+      </c>
+      <c r="G46">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>448</v>
+      </c>
+      <c r="B47">
+        <v>2030</v>
+      </c>
+      <c r="E47" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F47">
+        <v>78</v>
+      </c>
+      <c r="G47">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>448</v>
+      </c>
+      <c r="B48">
+        <v>2031</v>
+      </c>
+      <c r="E48" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F48">
+        <v>78</v>
+      </c>
+      <c r="G48">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>448</v>
+      </c>
+      <c r="B49">
+        <v>2032</v>
+      </c>
+      <c r="E49" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F49">
+        <v>78</v>
+      </c>
+      <c r="G49">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>448</v>
+      </c>
+      <c r="B50">
+        <v>2033</v>
+      </c>
+      <c r="E50" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F50">
+        <v>78</v>
+      </c>
+      <c r="G50">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>448</v>
+      </c>
+      <c r="B51">
+        <v>2034</v>
+      </c>
+      <c r="E51" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F51">
+        <v>78</v>
+      </c>
+      <c r="G51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>448</v>
+      </c>
+      <c r="B52">
+        <v>2035</v>
+      </c>
+      <c r="E52" s="5">
+        <v>11.023164556962024</v>
+      </c>
+      <c r="F52">
+        <v>78</v>
+      </c>
+      <c r="G52">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>452</v>
+      </c>
+      <c r="B53">
+        <v>2019</v>
+      </c>
+      <c r="D53">
+        <v>48</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>452</v>
+      </c>
+      <c r="B54">
+        <v>2020</v>
+      </c>
+      <c r="D54">
+        <v>48</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>452</v>
+      </c>
+      <c r="B55">
+        <v>2021</v>
+      </c>
+      <c r="D55">
+        <v>48</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>452</v>
+      </c>
+      <c r="B56">
+        <v>2022</v>
+      </c>
+      <c r="D56">
+        <v>48</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>452</v>
+      </c>
+      <c r="B57">
+        <v>2023</v>
+      </c>
+      <c r="D57">
+        <v>48</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>452</v>
+      </c>
+      <c r="B58">
+        <v>2024</v>
+      </c>
+      <c r="D58">
+        <v>48</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>452</v>
+      </c>
+      <c r="B59">
+        <v>2025</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>452</v>
+      </c>
+      <c r="B60">
+        <v>2026</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>452</v>
+      </c>
+      <c r="B61">
+        <v>2027</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>452</v>
+      </c>
+      <c r="B62">
+        <v>2028</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>452</v>
+      </c>
+      <c r="B63">
+        <v>2029</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>452</v>
+      </c>
+      <c r="B64">
+        <v>2030</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>452</v>
+      </c>
+      <c r="B65">
+        <v>2031</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>452</v>
+      </c>
+      <c r="B66">
+        <v>2032</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>452</v>
+      </c>
+      <c r="B67">
+        <v>2033</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>452</v>
+      </c>
+      <c r="B68">
+        <v>2034</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>452</v>
+      </c>
+      <c r="B69">
+        <v>2035</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>148</v>
+      </c>
+      <c r="B70">
+        <v>2019</v>
+      </c>
+      <c r="C70">
+        <v>28700</v>
+      </c>
+      <c r="D70">
+        <v>1440</v>
+      </c>
+      <c r="E70" s="5">
+        <f t="shared" ref="E70:E75" si="3">SUM(C70/D70)</f>
+        <v>19.930555555555557</v>
+      </c>
+      <c r="F70">
+        <v>74</v>
+      </c>
+      <c r="G70">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71">
+        <v>2020</v>
+      </c>
+      <c r="C71">
+        <v>28700</v>
+      </c>
+      <c r="D71">
+        <v>1440</v>
+      </c>
+      <c r="E71" s="5">
+        <f t="shared" si="3"/>
+        <v>19.930555555555557</v>
+      </c>
+      <c r="F71">
+        <v>74</v>
+      </c>
+      <c r="G71">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>148</v>
+      </c>
+      <c r="B72">
+        <v>2021</v>
+      </c>
+      <c r="C72">
+        <v>28700</v>
+      </c>
+      <c r="D72">
+        <v>1440</v>
+      </c>
+      <c r="E72" s="5">
+        <f t="shared" si="3"/>
+        <v>19.930555555555557</v>
+      </c>
+      <c r="F72">
+        <v>74</v>
+      </c>
+      <c r="G72">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>148</v>
+      </c>
+      <c r="B73">
+        <v>2022</v>
+      </c>
+      <c r="C73">
+        <v>28700</v>
+      </c>
+      <c r="D73">
+        <v>1440</v>
+      </c>
+      <c r="E73" s="5">
+        <f t="shared" si="3"/>
+        <v>19.930555555555557</v>
+      </c>
+      <c r="F73">
+        <v>74</v>
+      </c>
+      <c r="G73">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74">
+        <v>2023</v>
+      </c>
+      <c r="C74">
+        <v>28700</v>
+      </c>
+      <c r="D74">
+        <v>1440</v>
+      </c>
+      <c r="E74" s="5">
+        <f t="shared" si="3"/>
+        <v>19.930555555555557</v>
+      </c>
+      <c r="F74">
+        <v>74</v>
+      </c>
+      <c r="G74">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75">
+        <v>2024</v>
+      </c>
+      <c r="C75">
+        <v>28700</v>
+      </c>
+      <c r="D75">
+        <v>1440</v>
+      </c>
+      <c r="E75" s="5">
+        <f t="shared" si="3"/>
+        <v>19.930555555555557</v>
+      </c>
+      <c r="F75">
+        <v>74</v>
+      </c>
+      <c r="G75">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>148</v>
+      </c>
+      <c r="B76">
+        <v>2025</v>
+      </c>
+      <c r="E76" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F76">
+        <v>74</v>
+      </c>
+      <c r="G76">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>148</v>
+      </c>
+      <c r="B77">
+        <v>2026</v>
+      </c>
+      <c r="E77" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F77">
+        <v>74</v>
+      </c>
+      <c r="G77">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78">
+        <v>2027</v>
+      </c>
+      <c r="E78" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F78">
+        <v>74</v>
+      </c>
+      <c r="G78">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79">
+        <v>2028</v>
+      </c>
+      <c r="E79" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F79">
+        <v>74</v>
+      </c>
+      <c r="G79">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>148</v>
+      </c>
+      <c r="B80">
+        <v>2029</v>
+      </c>
+      <c r="E80" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F80">
+        <v>74</v>
+      </c>
+      <c r="G80">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>148</v>
+      </c>
+      <c r="B81">
+        <v>2030</v>
+      </c>
+      <c r="E81" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F81">
+        <v>74</v>
+      </c>
+      <c r="G81">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>148</v>
+      </c>
+      <c r="B82">
+        <v>2031</v>
+      </c>
+      <c r="E82" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F82">
+        <v>74</v>
+      </c>
+      <c r="G82">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>148</v>
+      </c>
+      <c r="B83">
+        <v>2032</v>
+      </c>
+      <c r="E83" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F83">
+        <v>74</v>
+      </c>
+      <c r="G83">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>148</v>
+      </c>
+      <c r="B84">
+        <v>2033</v>
+      </c>
+      <c r="E84" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F84">
+        <v>74</v>
+      </c>
+      <c r="G84">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>148</v>
+      </c>
+      <c r="B85">
+        <v>2034</v>
+      </c>
+      <c r="E85" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F85">
+        <v>74</v>
+      </c>
+      <c r="G85">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>148</v>
+      </c>
+      <c r="B86">
+        <v>2035</v>
+      </c>
+      <c r="E86" s="5">
+        <v>19.927670408517532</v>
+      </c>
+      <c r="F86">
+        <v>74</v>
+      </c>
+      <c r="G86">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A98B0489-E500-4DC5-923B-55378A814288}">
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
@@ -2188,7 +5834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E077DE-4CE7-480F-8724-0AA75B82F459}">
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2868,7 +6514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C22BF26-E06C-4F10-AF40-CB8CB98CC53D}">
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
@@ -2883,24 +6529,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
       <c r="D1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B2" s="4">
         <f>SUM(E2/D2)</f>
@@ -3032,37 +6678,37 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F1" t="s">
         <v>425</v>
       </c>
-      <c r="D1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E1" t="s">
-        <v>428</v>
-      </c>
-      <c r="F1" t="s">
-        <v>429</v>
-      </c>
       <c r="G1" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="K1" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="J1" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>158</v>
-      </c>
       <c r="L1" s="11" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -3089,7 +6735,7 @@
         <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -4073,120 +7719,120 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" t="s">
+        <v>126</v>
+      </c>
+      <c r="N1" t="s">
+        <v>362</v>
+      </c>
+      <c r="O1" t="s">
+        <v>363</v>
+      </c>
+      <c r="P1" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>128</v>
+      </c>
+      <c r="R1" t="s">
+        <v>129</v>
+      </c>
+      <c r="S1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T1" t="s">
+        <v>131</v>
+      </c>
+      <c r="U1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W1" t="s">
+        <v>134</v>
+      </c>
+      <c r="X1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>367</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD1" t="s">
         <v>139</v>
       </c>
-      <c r="B1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1" t="s">
-        <v>373</v>
-      </c>
-      <c r="D1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J1" t="s">
-        <v>129</v>
-      </c>
-      <c r="K1" t="s">
-        <v>126</v>
-      </c>
-      <c r="L1" t="s">
-        <v>127</v>
-      </c>
-      <c r="M1" t="s">
-        <v>128</v>
-      </c>
-      <c r="N1" t="s">
-        <v>366</v>
-      </c>
-      <c r="O1" t="s">
-        <v>367</v>
-      </c>
-      <c r="P1" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>130</v>
-      </c>
-      <c r="R1" t="s">
-        <v>131</v>
-      </c>
-      <c r="S1" t="s">
-        <v>132</v>
-      </c>
-      <c r="T1" t="s">
-        <v>133</v>
-      </c>
-      <c r="U1" t="s">
-        <v>134</v>
-      </c>
-      <c r="V1" t="s">
-        <v>135</v>
-      </c>
-      <c r="W1" t="s">
-        <v>136</v>
-      </c>
-      <c r="X1" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>138</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>369</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>370</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>371</v>
-      </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>140</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>141</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>142</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>143</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>144</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>145</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>146</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" s="10">
         <v>19</v>
@@ -4287,7 +7933,7 @@
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>33</v>
@@ -4388,7 +8034,7 @@
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>18</v>
@@ -4489,7 +8135,7 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>19</v>
@@ -4590,7 +8236,7 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>18</v>
@@ -4691,7 +8337,7 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>21</v>
@@ -4792,7 +8438,7 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -4893,7 +8539,7 @@
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>12</v>
@@ -4994,7 +8640,7 @@
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -5095,7 +8741,7 @@
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -5196,7 +8842,7 @@
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12">
         <v>8</v>
@@ -5297,7 +8943,7 @@
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13">
         <v>14</v>
@@ -5398,7 +9044,7 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -5499,7 +9145,7 @@
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <v>8</v>
@@ -5600,7 +9246,7 @@
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -5705,7 +9351,7 @@
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -5816,7 +9462,7 @@
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18">
         <v>15</v>
@@ -5929,7 +9575,7 @@
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -6048,7 +9694,7 @@
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B20">
         <v>16</v>
@@ -6173,7 +9819,7 @@
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>190</v>
@@ -6298,7 +9944,7 @@
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22">
         <v>283</v>
@@ -6423,7 +10069,7 @@
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B23">
         <v>305</v>
@@ -6548,7 +10194,7 @@
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B24">
         <v>231</v>
@@ -6673,7 +10319,7 @@
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B25">
         <v>199</v>
@@ -6798,7 +10444,7 @@
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B26">
         <v>169</v>
@@ -6923,7 +10569,7 @@
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B27">
         <v>177</v>
@@ -7048,7 +10694,7 @@
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B28">
         <v>155</v>
@@ -7173,7 +10819,7 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B29">
         <v>125</v>
@@ -7298,7 +10944,7 @@
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B30">
         <v>61</v>
@@ -7423,7 +11069,7 @@
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B31">
         <v>81</v>
@@ -7548,7 +11194,7 @@
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B32">
         <v>58</v>
@@ -7673,7 +11319,7 @@
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B33">
         <v>51</v>
@@ -7798,7 +11444,7 @@
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B34">
         <v>50</v>
@@ -7923,7 +11569,7 @@
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B35">
         <v>46</v>
@@ -8046,7 +11692,7 @@
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B36">
         <v>33</v>
@@ -8167,7 +11813,7 @@
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B37">
         <v>31</v>
@@ -8288,7 +11934,7 @@
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B38">
         <v>32</v>
@@ -8411,7 +12057,7 @@
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B39">
         <v>21</v>
@@ -8528,7 +12174,7 @@
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B40">
         <v>15</v>
@@ -8649,7 +12295,7 @@
     </row>
     <row r="41" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B41">
         <v>21</v>
@@ -8766,7 +12412,7 @@
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B42">
         <v>13</v>
@@ -8883,7 +12529,7 @@
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B43">
         <v>22</v>
@@ -9000,7 +12646,7 @@
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B44">
         <v>14</v>
@@ -9113,7 +12759,7 @@
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B45">
         <v>17</v>
@@ -9226,7 +12872,7 @@
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B46">
         <v>10</v>
@@ -9343,7 +12989,7 @@
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B47">
         <v>19</v>
@@ -9460,7 +13106,7 @@
     </row>
     <row r="48" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B48">
         <v>10</v>
@@ -9573,7 +13219,7 @@
     </row>
     <row r="49" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B49">
         <v>7</v>
@@ -9686,7 +13332,7 @@
     </row>
     <row r="50" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B50">
         <v>8</v>
@@ -9799,7 +13445,7 @@
     </row>
     <row r="51" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B51">
         <v>8</v>
@@ -9916,7 +13562,7 @@
     </row>
     <row r="52" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B52">
         <v>10</v>
@@ -10029,7 +13675,7 @@
     </row>
     <row r="53" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B53">
         <v>10</v>
@@ -10142,7 +13788,7 @@
     </row>
     <row r="54" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B54">
         <v>9</v>
@@ -10255,7 +13901,7 @@
     </row>
     <row r="55" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -10360,7 +14006,7 @@
     </row>
     <row r="56" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -10471,7 +14117,7 @@
     </row>
     <row r="57" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B57">
         <v>6</v>
@@ -10582,7 +14228,7 @@
     </row>
     <row r="58" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B58">
         <v>7</v>
@@ -10693,7 +14339,7 @@
     </row>
     <row r="59" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B59">
         <v>11</v>
@@ -10810,7 +14456,7 @@
     </row>
     <row r="60" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B60">
         <v>7</v>
@@ -10919,7 +14565,7 @@
     </row>
     <row r="61" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -11030,7 +14676,7 @@
     </row>
     <row r="62" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B62">
         <v>6</v>
@@ -11143,7 +14789,7 @@
     </row>
     <row r="63" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -11256,7 +14902,7 @@
     </row>
     <row r="64" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B64">
         <v>4</v>
@@ -11365,7 +15011,7 @@
     </row>
     <row r="65" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B65">
         <v>4</v>
@@ -11476,7 +15122,7 @@
     </row>
     <row r="66" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B66">
         <v>5</v>
@@ -11589,7 +15235,7 @@
     </row>
     <row r="67" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B67">
         <v>7</v>
@@ -11702,7 +15348,7 @@
     </row>
     <row r="68" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B68">
         <v>6</v>
@@ -11809,7 +15455,7 @@
     </row>
     <row r="69" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B69">
         <v>3</v>
@@ -11916,7 +15562,7 @@
     </row>
     <row r="70" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B70">
         <v>6</v>
@@ -12021,7 +15667,7 @@
     </row>
     <row r="71" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -12128,7 +15774,7 @@
     </row>
     <row r="72" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -12229,7 +15875,7 @@
     </row>
     <row r="73" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -12330,7 +15976,7 @@
     </row>
     <row r="74" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -12437,7 +16083,7 @@
     </row>
     <row r="75" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B75">
         <v>4</v>
@@ -12542,7 +16188,7 @@
     </row>
     <row r="76" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B76">
         <v>3</v>
@@ -12643,7 +16289,7 @@
     </row>
     <row r="77" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B77">
         <v>3</v>
@@ -12744,7 +16390,7 @@
     </row>
     <row r="78" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -12845,7 +16491,7 @@
     </row>
     <row r="79" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -12950,7 +16596,7 @@
     </row>
     <row r="80" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -13049,7 +16695,7 @@
     </row>
     <row r="81" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B81">
         <v>4</v>
@@ -13150,7 +16796,7 @@
     </row>
     <row r="82" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -13251,7 +16897,7 @@
     </row>
     <row r="83" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -13356,7 +17002,7 @@
     </row>
     <row r="84" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -13455,7 +17101,7 @@
     </row>
     <row r="85" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -13560,7 +17206,7 @@
     </row>
     <row r="86" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -13657,7 +17303,7 @@
     </row>
     <row r="87" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -13756,7 +17402,7 @@
     </row>
     <row r="88" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -13849,7 +17495,7 @@
     </row>
     <row r="89" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -13946,7 +17592,7 @@
     </row>
     <row r="90" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -14041,7 +17687,7 @@
     </row>
     <row r="91" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -14140,7 +17786,7 @@
     </row>
     <row r="92" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -14233,7 +17879,7 @@
     </row>
     <row r="93" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -14328,7 +17974,7 @@
     </row>
     <row r="94" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -14421,7 +18067,7 @@
     </row>
     <row r="95" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -14514,7 +18160,7 @@
     </row>
     <row r="96" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -14603,7 +18249,7 @@
     </row>
     <row r="97" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -14696,7 +18342,7 @@
     </row>
     <row r="98" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -14785,7 +18431,7 @@
     </row>
     <row r="99" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -14874,7 +18520,7 @@
     </row>
     <row r="100" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -14967,7 +18613,7 @@
     </row>
     <row r="101" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -15056,7 +18702,7 @@
     </row>
     <row r="102" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -15145,7 +18791,7 @@
     </row>
     <row r="103" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B103">
         <v>2862</v>
@@ -15388,39 +19034,39 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" t="s">
         <v>159</v>
       </c>
-      <c r="B1" t="s">
-        <v>161</v>
-      </c>
       <c r="C1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F1" t="s">
         <v>184</v>
       </c>
-      <c r="E1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F1" t="s">
-        <v>186</v>
-      </c>
       <c r="G1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1" t="s">
         <v>201</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>202</v>
-      </c>
-      <c r="I1" t="s">
-        <v>203</v>
-      </c>
-      <c r="J1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B2">
         <v>207</v>
@@ -15432,21 +19078,21 @@
         <v>50</v>
       </c>
       <c r="G2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I2" t="s">
+        <v>220</v>
+      </c>
+      <c r="J2" t="s">
         <v>230</v>
-      </c>
-      <c r="H2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I2" t="s">
-        <v>222</v>
-      </c>
-      <c r="J2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B3">
         <v>38</v>
@@ -15458,21 +19104,21 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H3" t="s">
         <v>231</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J3" t="s">
         <v>233</v>
-      </c>
-      <c r="I3" t="s">
-        <v>234</v>
-      </c>
-      <c r="J3" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B4">
         <v>1280</v>
@@ -15484,21 +19130,21 @@
         <v>100</v>
       </c>
       <c r="G4" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I4" t="s">
         <v>220</v>
       </c>
-      <c r="H4" t="s">
-        <v>228</v>
-      </c>
-      <c r="I4" t="s">
-        <v>222</v>
-      </c>
       <c r="J4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B5">
         <v>389</v>
@@ -15510,21 +19156,21 @@
         <v>30</v>
       </c>
       <c r="G5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J5" t="s">
         <v>219</v>
-      </c>
-      <c r="H5" t="s">
-        <v>220</v>
-      </c>
-      <c r="I5" t="s">
-        <v>215</v>
-      </c>
-      <c r="J5" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B6">
         <v>2067</v>
@@ -15536,21 +19182,21 @@
         <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B7">
         <v>351</v>
@@ -15562,21 +19208,21 @@
         <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H7" t="s">
+        <v>218</v>
+      </c>
+      <c r="I7" t="s">
         <v>220</v>
       </c>
-      <c r="I7" t="s">
-        <v>222</v>
-      </c>
       <c r="J7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B8">
         <v>102</v>
@@ -15588,21 +19234,21 @@
         <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H8" t="s">
+        <v>234</v>
+      </c>
+      <c r="I8" t="s">
+        <v>235</v>
+      </c>
+      <c r="J8" t="s">
         <v>236</v>
-      </c>
-      <c r="I8" t="s">
-        <v>237</v>
-      </c>
-      <c r="J8" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B9">
         <v>5604</v>
@@ -15614,21 +19260,21 @@
         <v>90</v>
       </c>
       <c r="G9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H9" t="s">
+        <v>204</v>
+      </c>
+      <c r="I9" t="s">
         <v>205</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>206</v>
-      </c>
-      <c r="I9" t="s">
-        <v>207</v>
-      </c>
-      <c r="J9" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B10">
         <v>531</v>
@@ -15640,21 +19286,21 @@
         <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B11">
         <v>3597</v>
@@ -15666,21 +19312,21 @@
         <v>100</v>
       </c>
       <c r="G11" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" t="s">
+        <v>212</v>
+      </c>
+      <c r="I11" t="s">
         <v>213</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>214</v>
-      </c>
-      <c r="I11" t="s">
-        <v>215</v>
-      </c>
-      <c r="J11" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B12">
         <v>352</v>
@@ -15692,21 +19338,21 @@
         <v>100</v>
       </c>
       <c r="G12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B13">
         <v>4057</v>
@@ -15718,21 +19364,21 @@
         <v>100</v>
       </c>
       <c r="G13" t="s">
+        <v>207</v>
+      </c>
+      <c r="H13" t="s">
+        <v>208</v>
+      </c>
+      <c r="I13" t="s">
         <v>209</v>
       </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
         <v>210</v>
-      </c>
-      <c r="I13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J13" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B14">
         <v>221</v>
@@ -15744,21 +19390,21 @@
         <v>30</v>
       </c>
       <c r="G14" t="s">
+        <v>257</v>
+      </c>
+      <c r="H14" t="s">
+        <v>258</v>
+      </c>
+      <c r="I14" t="s">
         <v>259</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>260</v>
-      </c>
-      <c r="I14" t="s">
-        <v>261</v>
-      </c>
-      <c r="J14" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B15">
         <v>17</v>
@@ -15770,21 +19416,21 @@
         <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H15" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J15" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B16">
         <v>275</v>
@@ -15796,21 +19442,21 @@
         <v>85</v>
       </c>
       <c r="G16" t="s">
+        <v>237</v>
+      </c>
+      <c r="H16" t="s">
+        <v>229</v>
+      </c>
+      <c r="I16" t="s">
+        <v>238</v>
+      </c>
+      <c r="J16" t="s">
         <v>239</v>
-      </c>
-      <c r="H16" t="s">
-        <v>231</v>
-      </c>
-      <c r="I16" t="s">
-        <v>240</v>
-      </c>
-      <c r="J16" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B17">
         <v>33</v>
@@ -15822,21 +19468,21 @@
         <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J17" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B18">
         <v>11</v>
@@ -15848,21 +19494,21 @@
         <v>10</v>
       </c>
       <c r="G18" t="s">
+        <v>287</v>
+      </c>
+      <c r="H18" t="s">
+        <v>288</v>
+      </c>
+      <c r="I18" t="s">
+        <v>259</v>
+      </c>
+      <c r="J18" t="s">
         <v>289</v>
-      </c>
-      <c r="H18" t="s">
-        <v>290</v>
-      </c>
-      <c r="I18" t="s">
-        <v>261</v>
-      </c>
-      <c r="J18" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B19">
         <v>261</v>
@@ -15874,21 +19520,21 @@
         <v>10</v>
       </c>
       <c r="G19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I19" t="s">
         <v>248</v>
       </c>
-      <c r="H19" t="s">
+      <c r="J19" t="s">
         <v>249</v>
-      </c>
-      <c r="I19" t="s">
-        <v>250</v>
-      </c>
-      <c r="J19" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B20">
         <v>66</v>
@@ -15900,21 +19546,21 @@
         <v>80</v>
       </c>
       <c r="G20" t="s">
+        <v>243</v>
+      </c>
+      <c r="H20" t="s">
+        <v>244</v>
+      </c>
+      <c r="I20" t="s">
+        <v>232</v>
+      </c>
+      <c r="J20" t="s">
         <v>245</v>
-      </c>
-      <c r="H20" t="s">
-        <v>246</v>
-      </c>
-      <c r="I20" t="s">
-        <v>234</v>
-      </c>
-      <c r="J20" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B21">
         <v>19</v>
@@ -15926,21 +19572,21 @@
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B22">
         <v>102</v>
@@ -15952,21 +19598,21 @@
         <v>5</v>
       </c>
       <c r="G22" t="s">
+        <v>253</v>
+      </c>
+      <c r="H22" t="s">
+        <v>254</v>
+      </c>
+      <c r="I22" t="s">
         <v>255</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>256</v>
-      </c>
-      <c r="I22" t="s">
-        <v>257</v>
-      </c>
-      <c r="J22" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B23">
         <v>32</v>
@@ -15978,21 +19624,21 @@
         <v>75</v>
       </c>
       <c r="G23" t="s">
+        <v>282</v>
+      </c>
+      <c r="H23" t="s">
+        <v>283</v>
+      </c>
+      <c r="I23" t="s">
         <v>284</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" t="s">
         <v>285</v>
-      </c>
-      <c r="I23" t="s">
-        <v>286</v>
-      </c>
-      <c r="J23" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B24">
         <v>133</v>
@@ -16004,21 +19650,21 @@
         <v>40</v>
       </c>
       <c r="G24" t="s">
+        <v>250</v>
+      </c>
+      <c r="H24" t="s">
+        <v>251</v>
+      </c>
+      <c r="I24" t="s">
+        <v>232</v>
+      </c>
+      <c r="J24" t="s">
         <v>252</v>
-      </c>
-      <c r="H24" t="s">
-        <v>253</v>
-      </c>
-      <c r="I24" t="s">
-        <v>234</v>
-      </c>
-      <c r="J24" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B25">
         <v>28</v>
@@ -16030,21 +19676,21 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
+        <v>262</v>
+      </c>
+      <c r="H25" t="s">
+        <v>263</v>
+      </c>
+      <c r="I25" t="s">
         <v>264</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" t="s">
         <v>265</v>
-      </c>
-      <c r="I25" t="s">
-        <v>266</v>
-      </c>
-      <c r="J25" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B26">
         <v>101</v>
@@ -16056,21 +19702,21 @@
         <v>60</v>
       </c>
       <c r="G26" t="s">
+        <v>240</v>
+      </c>
+      <c r="H26" t="s">
+        <v>241</v>
+      </c>
+      <c r="I26" t="s">
+        <v>232</v>
+      </c>
+      <c r="J26" t="s">
         <v>242</v>
-      </c>
-      <c r="H26" t="s">
-        <v>243</v>
-      </c>
-      <c r="I26" t="s">
-        <v>234</v>
-      </c>
-      <c r="J26" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B27">
         <v>11</v>
@@ -16082,21 +19728,21 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
+        <v>310</v>
+      </c>
+      <c r="H27" t="s">
+        <v>263</v>
+      </c>
+      <c r="I27" t="s">
+        <v>311</v>
+      </c>
+      <c r="J27" t="s">
         <v>312</v>
-      </c>
-      <c r="H27" t="s">
-        <v>265</v>
-      </c>
-      <c r="I27" t="s">
-        <v>313</v>
-      </c>
-      <c r="J27" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B28">
         <v>615</v>
@@ -16108,21 +19754,21 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
+        <v>269</v>
+      </c>
+      <c r="H28" t="s">
+        <v>270</v>
+      </c>
+      <c r="I28" t="s">
         <v>271</v>
       </c>
-      <c r="H28" t="s">
-        <v>272</v>
-      </c>
-      <c r="I28" t="s">
-        <v>273</v>
-      </c>
       <c r="J28" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B29">
         <v>42</v>
@@ -16134,21 +19780,21 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H29" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I29" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B30">
         <v>169</v>
@@ -16160,21 +19806,21 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
+        <v>276</v>
+      </c>
+      <c r="H30" t="s">
+        <v>277</v>
+      </c>
+      <c r="I30" t="s">
+        <v>274</v>
+      </c>
+      <c r="J30" t="s">
         <v>278</v>
-      </c>
-      <c r="H30" t="s">
-        <v>279</v>
-      </c>
-      <c r="I30" t="s">
-        <v>276</v>
-      </c>
-      <c r="J30" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B31">
         <v>104</v>
@@ -16186,21 +19832,21 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
+        <v>279</v>
+      </c>
+      <c r="H31" t="s">
+        <v>280</v>
+      </c>
+      <c r="I31" t="s">
         <v>281</v>
       </c>
-      <c r="H31" t="s">
-        <v>282</v>
-      </c>
-      <c r="I31" t="s">
-        <v>283</v>
-      </c>
       <c r="J31" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B32">
         <v>37</v>
@@ -16212,21 +19858,21 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
+        <v>317</v>
+      </c>
+      <c r="H32" t="s">
+        <v>318</v>
+      </c>
+      <c r="I32" t="s">
         <v>319</v>
       </c>
-      <c r="H32" t="s">
+      <c r="J32" t="s">
         <v>320</v>
-      </c>
-      <c r="I32" t="s">
-        <v>321</v>
-      </c>
-      <c r="J32" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B33">
         <v>27</v>
@@ -16238,21 +19884,21 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
+        <v>321</v>
+      </c>
+      <c r="H33" t="s">
+        <v>322</v>
+      </c>
+      <c r="I33" t="s">
         <v>323</v>
       </c>
-      <c r="H33" t="s">
+      <c r="J33" t="s">
         <v>324</v>
-      </c>
-      <c r="I33" t="s">
-        <v>325</v>
-      </c>
-      <c r="J33" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B34">
         <v>105</v>
@@ -16264,21 +19910,21 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
+        <v>290</v>
+      </c>
+      <c r="H34" t="s">
         <v>292</v>
       </c>
-      <c r="H34" t="s">
-        <v>294</v>
-      </c>
       <c r="I34" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J34" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B35">
         <v>79</v>
@@ -16290,21 +19936,21 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H35" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I35" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J35" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B36">
         <v>35</v>
@@ -16316,21 +19962,21 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
+        <v>272</v>
+      </c>
+      <c r="H36" t="s">
+        <v>276</v>
+      </c>
+      <c r="I36" t="s">
         <v>274</v>
       </c>
-      <c r="H36" t="s">
-        <v>278</v>
-      </c>
-      <c r="I36" t="s">
-        <v>276</v>
-      </c>
       <c r="J36" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B37">
         <v>23</v>
@@ -16342,21 +19988,21 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H37" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I37" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J37" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B38">
         <v>36</v>
@@ -16368,21 +20014,21 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
+        <v>272</v>
+      </c>
+      <c r="H38" t="s">
+        <v>273</v>
+      </c>
+      <c r="I38" t="s">
         <v>274</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
         <v>275</v>
-      </c>
-      <c r="I38" t="s">
-        <v>276</v>
-      </c>
-      <c r="J38" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B39">
         <v>43</v>
@@ -16394,16 +20040,16 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
+        <v>266</v>
+      </c>
+      <c r="H39" t="s">
+        <v>267</v>
+      </c>
+      <c r="I39" t="s">
         <v>268</v>
       </c>
-      <c r="H39" t="s">
-        <v>269</v>
-      </c>
-      <c r="I39" t="s">
-        <v>270</v>
-      </c>
       <c r="J39" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -16417,280 +20063,329 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E1" t="s">
         <v>350</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>351</v>
       </c>
-      <c r="C1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B2" t="s">
         <v>352</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B3" t="s">
         <v>353</v>
       </c>
-      <c r="F1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>334</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C5" t="s">
+        <v>335</v>
+      </c>
+      <c r="D5" t="s">
+        <v>428</v>
+      </c>
+      <c r="E5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C6" t="s">
+        <v>433</v>
+      </c>
+      <c r="D6" t="s">
+        <v>429</v>
+      </c>
+      <c r="E6" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C8" t="s">
+        <v>433</v>
+      </c>
+      <c r="D8" t="s">
+        <v>429</v>
+      </c>
+      <c r="E8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>339</v>
+      </c>
+      <c r="B9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D9" t="s">
+        <v>430</v>
+      </c>
+      <c r="E9" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B10" t="s">
+        <v>340</v>
+      </c>
+      <c r="C10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D10" t="s">
+        <v>430</v>
+      </c>
+      <c r="E10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F10" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>341</v>
+      </c>
+      <c r="B11" t="s">
         <v>354</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C11" t="s">
+        <v>434</v>
+      </c>
+      <c r="D11" t="s">
+        <v>429</v>
+      </c>
+      <c r="E11" t="s">
+        <v>357</v>
+      </c>
+      <c r="F11" t="s">
         <v>360</v>
       </c>
-      <c r="D2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" t="s">
+        <v>434</v>
+      </c>
+      <c r="D12" t="s">
+        <v>430</v>
+      </c>
+      <c r="E12" t="s">
+        <v>358</v>
+      </c>
+      <c r="F12" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>343</v>
+      </c>
+      <c r="B13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C13" t="s">
+        <v>343</v>
+      </c>
+      <c r="D13" t="s">
+        <v>429</v>
+      </c>
+      <c r="E13" t="s">
+        <v>358</v>
+      </c>
+      <c r="G13" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>344</v>
+      </c>
+      <c r="B14" t="s">
+        <v>344</v>
+      </c>
+      <c r="C14" t="s">
+        <v>344</v>
+      </c>
+      <c r="D14" t="s">
+        <v>429</v>
+      </c>
+      <c r="E14" t="s">
+        <v>357</v>
+      </c>
+      <c r="G14" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B15" t="s">
+        <v>345</v>
+      </c>
+      <c r="C15" t="s">
+        <v>345</v>
+      </c>
+      <c r="D15" t="s">
+        <v>429</v>
+      </c>
+      <c r="E15" t="s">
+        <v>358</v>
+      </c>
+      <c r="G15" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>346</v>
+      </c>
+      <c r="B16" t="s">
+        <v>346</v>
+      </c>
+      <c r="C16" t="s">
+        <v>433</v>
+      </c>
+      <c r="D16" t="s">
+        <v>429</v>
+      </c>
+      <c r="E16" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>347</v>
+      </c>
+      <c r="B17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C17" t="s">
         <v>355</v>
       </c>
-      <c r="C3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B4" t="s">
-        <v>355</v>
-      </c>
-      <c r="C4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D4" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>337</v>
-      </c>
-      <c r="B5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C5" t="s">
-        <v>337</v>
-      </c>
-      <c r="D5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>338</v>
-      </c>
-      <c r="B6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C6" t="s">
-        <v>357</v>
-      </c>
-      <c r="D6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>339</v>
-      </c>
-      <c r="B7" t="s">
-        <v>339</v>
-      </c>
-      <c r="C7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>340</v>
-      </c>
-      <c r="B8" t="s">
-        <v>340</v>
-      </c>
-      <c r="C8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D8" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>341</v>
-      </c>
-      <c r="B9" t="s">
-        <v>341</v>
-      </c>
-      <c r="C9" t="s">
-        <v>358</v>
-      </c>
-      <c r="D9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E9" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>342</v>
-      </c>
-      <c r="B10" t="s">
-        <v>342</v>
-      </c>
-      <c r="C10" t="s">
-        <v>358</v>
-      </c>
-      <c r="D10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E10" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>343</v>
-      </c>
-      <c r="B11" t="s">
-        <v>356</v>
-      </c>
-      <c r="C11" t="s">
-        <v>358</v>
-      </c>
-      <c r="D11" t="s">
-        <v>362</v>
-      </c>
-      <c r="E11" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>344</v>
-      </c>
-      <c r="B12" t="s">
-        <v>356</v>
-      </c>
-      <c r="C12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D12" t="s">
-        <v>362</v>
-      </c>
-      <c r="E12" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>345</v>
-      </c>
-      <c r="B13" t="s">
-        <v>345</v>
-      </c>
-      <c r="C13" t="s">
-        <v>345</v>
-      </c>
-      <c r="D13" t="s">
-        <v>361</v>
-      </c>
-      <c r="F13" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>346</v>
-      </c>
-      <c r="B14" t="s">
-        <v>346</v>
-      </c>
-      <c r="C14" t="s">
-        <v>346</v>
-      </c>
-      <c r="D14" t="s">
-        <v>361</v>
-      </c>
-      <c r="F14" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>347</v>
-      </c>
-      <c r="B15" t="s">
-        <v>347</v>
-      </c>
-      <c r="C15" t="s">
-        <v>347</v>
-      </c>
-      <c r="D15" t="s">
-        <v>361</v>
-      </c>
-      <c r="F15" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>348</v>
-      </c>
-      <c r="B16" t="s">
-        <v>348</v>
-      </c>
-      <c r="C16" t="s">
-        <v>357</v>
-      </c>
-      <c r="D16" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>349</v>
-      </c>
-      <c r="B17" t="s">
-        <v>349</v>
-      </c>
-      <c r="C17" t="s">
-        <v>359</v>
-      </c>
-      <c r="D17" t="s">
-        <v>298</v>
+      <c r="E17" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -16719,19 +20414,19 @@
         <v>2</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -16739,10 +20434,10 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D2">
         <v>500</v>
@@ -16751,7 +20446,7 @@
         <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -16759,10 +20454,10 @@
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D3">
         <v>750</v>
@@ -16771,7 +20466,7 @@
         <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -16779,10 +20474,10 @@
         <v>2027</v>
       </c>
       <c r="B4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D4">
         <v>750</v>
@@ -16796,10 +20491,10 @@
         <v>2027</v>
       </c>
       <c r="B5" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D5">
         <v>50</v>
@@ -16813,10 +20508,10 @@
         <v>2028</v>
       </c>
       <c r="B6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -16830,10 +20525,10 @@
         <v>2033</v>
       </c>
       <c r="B7" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -16864,66 +20559,66 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -16947,110 +20642,110 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C2" t="s">
         <v>393</v>
       </c>
-      <c r="C2" t="s">
-        <v>397</v>
-      </c>
       <c r="D2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C4" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B5" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C5" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D6" t="s">
         <v>408</v>
-      </c>
-      <c r="B6" t="s">
-        <v>415</v>
-      </c>
-      <c r="D6" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D7" t="s">
         <v>409</v>
-      </c>
-      <c r="B7" t="s">
-        <v>415</v>
-      </c>
-      <c r="D7" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B8">
         <v>30000</v>
       </c>
       <c r="D8" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B9">
         <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
